--- a/nr-add-cip/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/nr-add-cip/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:39+00:00</t>
+    <t>2026-02-02T15:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-cip/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/nr-add-cip/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:16+00:00</t>
+    <t>2026-02-23T08:39:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
